--- a/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
+++ b/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,19 +76,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00111111"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00111A2D"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C41E3A"/>
+      <color rgb="00111111"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C41E3A"/>
+      <color rgb="00111111"/>
       <sz val="14"/>
     </font>
     <font>
@@ -104,7 +110,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -123,7 +129,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF5F5"/>
+        <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,11 +140,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -187,13 +188,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -201,15 +202,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
+++ b/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
@@ -65,13 +65,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00151A22"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00151A22"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -99,15 +99,14 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="005F6874"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00111A2D"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="0094A3B8"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -186,7 +185,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -201,16 +200,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,12 +577,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D26"/>
+  <dimension ref="B2:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -595,14 +596,14 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Operación mensual de cuentas orgánicas + estructura</t>
+          <t>Estructura actual · operación mensual</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Red Humana, Espartanos, Laboratorio Bots, Staff y Equipo de Gerencia</t>
+          <t>Sin líneas de personal/staff ni equipo de gerencia · conceptos de organigrama</t>
         </is>
       </c>
     </row>
@@ -636,160 +637,150 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="B9" s="8" t="n">
-        <v>9000</v>
+        <v>1</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>RED HUMANA (operación mensual)</t>
+          <t>GERENCIA GENERAL</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>29850</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
+        <v>8450</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="B10" s="8" t="n">
-        <v>3000</v>
+        <v>24</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>BOTS ORIGINALES (mantenimiento mensual)</t>
+          <t>GERENCIAS REGIONALES (4 gerentes x 6 regiones)</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>15450</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="B11" s="8" t="n">
-        <v>500</v>
+        <v>1512</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ESPARTANOS (operación elite mensual)</t>
+          <t>ESTRUCTURA OPERATIVA (24 gerencias x 63 personas)</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
+        <v>22848</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="B12" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>LABORATORIO BOTS (soporte mensual)</t>
+          <t>CUENTAS POR PERSONA (capacidad operativa)</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>4248</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="B13" s="8" t="n">
-        <v>12</v>
+        <v>15120</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>STAFF (operación mensual)</t>
+          <t>META DE CUENTAS (1.512 personas x 10 cuentas)</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>3148</v>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="B14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>EQUIPO GERENCIA (dirección mensual)</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>TOTAL GERENCIA MENSUAL</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="12" t="n">
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="12" t="n">
         <v>64248</v>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+    </row>
     <row r="18">
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>RESUMEN</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Inversión mensual</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="16" t="n">
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="16" t="n">
         <v>64248</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Referencia estructura: estatus actual 9.634 cuentas · 63,72% avance · 5.486 por alcanzar (sin costo adicional en este presupuesto).</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Condiciones</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>• Presupuesto de gerencia mensual Yellowstone (operación continua).
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>• Conceptos alineados al organigrama. Se eliminaron gastos de personal/staff y equipo de gerencia.
 • Validez del presupuesto: 15 días. Montos en dólares estadounidenses (USD).
 • Total gerencia mensual: USD 64,248.</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>YELLOWSTONE · Gerencia mensual · 1 hoja</t>
-        </is>
-      </c>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B22:D24"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B23:D25"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
+++ b/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
@@ -185,7 +185,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -204,9 +204,7 @@
     <xf numFmtId="164" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -582,7 +580,7 @@
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -603,7 +601,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sin líneas de personal/staff ni equipo de gerencia · conceptos de organigrama</t>
+          <t>Conceptos del organigrama (sin líneas de personal ni gerencia operativa)</t>
         </is>
       </c>
     </row>
@@ -637,7 +635,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="26" customHeight="1">
       <c r="B9" s="8" t="n">
         <v>1</v>
       </c>
@@ -650,52 +648,52 @@
         <v>8450</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="26" customHeight="1">
       <c r="B10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>GERENCIAS REGIONALES (4 gerentes x 6 regiones)</t>
+          <t>GERENCIAS REGIONALES (4 x 6 regiones)</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
         <v>18600</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="B11" s="8" t="n">
         <v>1512</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ESTRUCTURA OPERATIVA (24 gerencias x 63 personas)</t>
+          <t>ESTRUCTURA OPERATIVA (24 x 63)</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
         <v>22848</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
       <c r="B12" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>CUENTAS POR PERSONA (capacidad operativa)</t>
+          <t>CUENTAS POR PERSONA (capacidad)</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
         <v>9200</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="26" customHeight="1">
       <c r="B13" s="8" t="n">
         <v>15120</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>META DE CUENTAS (1.512 personas x 10 cuentas)</t>
+          <t>META DE CUENTAS (1.512 x 10)</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
@@ -733,10 +731,10 @@
         <v>64248</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20">
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Referencia estructura: estatus actual 9.634 cuentas · 63,72% avance · 5.486 por alcanzar (sin costo adicional en este presupuesto).</t>
+          <t>Referencia: estatus 9.634 cuentas · 63,72% avance · 5.486 por alcanzar (sin costo extra).</t>
         </is>
       </c>
       <c r="C20" s="18" t="n"/>
@@ -752,7 +750,7 @@
     <row r="23">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>• Conceptos alineados al organigrama. Se eliminaron gastos de personal/staff y equipo de gerencia.
+          <t>• Conceptos alineados al organigrama de estructura actual.
 • Validez del presupuesto: 15 días. Montos en dólares estadounidenses (USD).
 • Total gerencia mensual: USD 64,248.</t>
         </is>

--- a/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
+++ b/docs/presupuesto-yellowstone-gerencia-mensual.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D25"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -601,7 +601,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Conceptos del organigrama (sin líneas de personal ni gerencia operativa)</t>
+          <t>Conceptos del organigrama (sin cuentas por persona ni meta de cuentas)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>8450</v>
+        <v>11450</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>18600</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -671,114 +671,88 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>22848</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>CUENTAS POR PERSONA (capacidad)</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>9200</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="8" t="n">
-        <v>15120</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>META DE CUENTAS (1.512 x 10)</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>5150</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="11" t="inlineStr">
+        <v>29198</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>TOTAL GERENCIA MENSUAL</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="12" t="n">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="12" t="n">
         <v>64248</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="13" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Inversión mensual</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="16" t="n">
+        <v>64248</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Inversión mensual</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="16" t="n">
-        <v>64248</v>
-      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Referencia: estatus 9.634 cuentas · 63,72% avance · 5.486 por alcanzar (sin costo extra).</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Referencia: estatus 9.634 cuentas · 63,72% avance · 5.486 por alcanzar (sin costo extra).</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Condiciones</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>• Conceptos alineados al organigrama de estructura actual.
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>• Sin líneas de cuentas por persona ni meta de cuentas; monto redistribuido.
 • Validez del presupuesto: 15 días. Montos en dólares estadounidenses (USD).
 • Total gerencia mensual: USD 64,248.</t>
         </is>
       </c>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="18" t="n"/>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="18" t="n"/>
     </row>
-    <row r="24">
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B23:D25"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B21:D23"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
